--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_14.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:M148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4505 +469,6645 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:20.916</t>
+          <t>2026-05-29 09:40:42.289</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779421942970</v>
+        <v>1780022439343</v>
       </c>
       <c r="C2" t="n">
-        <v>86292</v>
+        <v>84132</v>
       </c>
       <c r="D2" t="n">
-        <v>-364.5</v>
+        <v>-91.88</v>
       </c>
       <c r="E2" t="n">
         <v>81</v>
       </c>
       <c r="F2" t="n">
-        <v>805</v>
+        <v>2319</v>
       </c>
       <c r="G2" t="n">
-        <v>49.71</v>
+        <v>279.59</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2946</v>
+      </c>
+      <c r="L2" t="n">
+        <v>110</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.654</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:21.595</t>
+          <t>2026-05-29 09:40:42.291</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779421943172</v>
+        <v>1780022439543</v>
       </c>
       <c r="C3" t="n">
-        <v>86569</v>
+        <v>84014</v>
       </c>
       <c r="D3" t="n">
-        <v>-69.27</v>
+        <v>-205.29</v>
       </c>
       <c r="E3" t="n">
         <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>805</v>
+        <v>2319</v>
       </c>
       <c r="G3" t="n">
-        <v>49.71</v>
+        <v>279.59</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J3" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2746</v>
+      </c>
+      <c r="L3" t="n">
+        <v>110</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.205</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:21.596</t>
+          <t>2026-05-29 09:40:42.292</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779421943373</v>
+        <v>1780022439762</v>
       </c>
       <c r="C4" t="n">
-        <v>86858</v>
+        <v>83395</v>
       </c>
       <c r="D4" t="n">
-        <v>223.19</v>
+        <v>-814.02</v>
       </c>
       <c r="E4" t="n">
         <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>805</v>
+        <v>2319</v>
       </c>
       <c r="G4" t="n">
-        <v>49.71</v>
+        <v>279.59</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2529</v>
+      </c>
+      <c r="L4" t="n">
+        <v>111</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.828</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:21.596</t>
+          <t>2026-05-29 09:40:42.293</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779421943575</v>
+        <v>1780022439962</v>
       </c>
       <c r="C5" t="n">
-        <v>87158</v>
+        <v>84768</v>
       </c>
       <c r="D5" t="n">
-        <v>512.03</v>
+        <v>599.6799999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
-        <v>685</v>
+        <v>2319</v>
       </c>
       <c r="G5" t="n">
-        <v>50.91</v>
+        <v>279.59</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2330</v>
+      </c>
+      <c r="L5" t="n">
+        <v>108</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:21.599</t>
+          <t>2026-05-29 09:40:42.294</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779421943776</v>
+        <v>1780022440162</v>
       </c>
       <c r="C6" t="n">
-        <v>86304</v>
+        <v>83497</v>
       </c>
       <c r="D6" t="n">
-        <v>-367.57</v>
+        <v>-701.3</v>
       </c>
       <c r="E6" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F6" t="n">
-        <v>685</v>
+        <v>2319</v>
       </c>
       <c r="G6" t="n">
-        <v>50.91</v>
+        <v>279.59</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2131</v>
+      </c>
+      <c r="L6" t="n">
+        <v>109</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.092</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:21.992</t>
+          <t>2026-05-29 09:40:42.464</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779421943977</v>
+        <v>1780022440362</v>
       </c>
       <c r="C7" t="n">
-        <v>86671</v>
+        <v>81876</v>
       </c>
       <c r="D7" t="n">
-        <v>17.81</v>
+        <v>-2287.24</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>685</v>
+        <v>2319</v>
       </c>
       <c r="G7" t="n">
-        <v>50.91</v>
+        <v>279.59</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2101</v>
+      </c>
+      <c r="L7" t="n">
+        <v>107</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.303</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:21.998</t>
+          <t>2026-05-29 09:40:42.466</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779421944179</v>
+        <v>1780022440562</v>
       </c>
       <c r="C8" t="n">
-        <v>87111</v>
+        <v>81506</v>
       </c>
       <c r="D8" t="n">
-        <v>456.92</v>
+        <v>-2542.88</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
-        <v>685</v>
+        <v>2319</v>
       </c>
       <c r="G8" t="n">
-        <v>48.68</v>
+        <v>279.59</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1903</v>
+      </c>
+      <c r="L8" t="n">
+        <v>107</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.959</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:22.411</t>
+          <t>2026-05-29 09:40:42.467</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779421944380</v>
+        <v>1780022440762</v>
       </c>
       <c r="C9" t="n">
-        <v>86868</v>
+        <v>81964</v>
       </c>
       <c r="D9" t="n">
-        <v>191.07</v>
+        <v>-1957.73</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
-        <v>685</v>
+        <v>2319</v>
       </c>
       <c r="G9" t="n">
-        <v>48.68</v>
+        <v>279.59</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1704</v>
+      </c>
+      <c r="L9" t="n">
+        <v>108</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.833</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:22.412</t>
+          <t>2026-05-29 09:40:42.470</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779421944582</v>
+        <v>1780022440962</v>
       </c>
       <c r="C10" t="n">
-        <v>86137</v>
+        <v>84039</v>
       </c>
       <c r="D10" t="n">
-        <v>-549.48</v>
+        <v>215.15</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F10" t="n">
-        <v>685</v>
+        <v>2319</v>
       </c>
       <c r="G10" t="n">
-        <v>48.68</v>
+        <v>279.59</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1507</v>
+      </c>
+      <c r="L10" t="n">
+        <v>112</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.117</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:22.918</t>
+          <t>2026-05-29 09:40:42.482</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779421944783</v>
+        <v>1780022441162</v>
       </c>
       <c r="C11" t="n">
-        <v>86316</v>
+        <v>83930</v>
       </c>
       <c r="D11" t="n">
-        <v>-343.01</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F11" t="n">
-        <v>685</v>
+        <v>2319</v>
       </c>
       <c r="G11" t="n">
-        <v>48.68</v>
+        <v>279.59</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1318</v>
+      </c>
+      <c r="L11" t="n">
+        <v>108</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.733</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:22.923</t>
+          <t>2026-05-29 09:40:42.496</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779421944984</v>
+        <v>1780022441381</v>
       </c>
       <c r="C12" t="n">
-        <v>86571</v>
+        <v>83216</v>
       </c>
       <c r="D12" t="n">
-        <v>-70.86</v>
+        <v>-623.37</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F12" t="n">
-        <v>685</v>
+        <v>2319</v>
       </c>
       <c r="G12" t="n">
-        <v>48.68</v>
+        <v>279.59</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1114</v>
+      </c>
+      <c r="L12" t="n">
+        <v>107</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.064</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:23.215</t>
+          <t>2026-05-29 09:40:42.527</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779421945186</v>
+        <v>1780022441581</v>
       </c>
       <c r="C13" t="n">
-        <v>85884</v>
+        <v>83727</v>
       </c>
       <c r="D13" t="n">
-        <v>-754.3099999999999</v>
+        <v>-81.20999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F13" t="n">
-        <v>685</v>
+        <v>2319</v>
       </c>
       <c r="G13" t="n">
-        <v>48.68</v>
+        <v>279.59</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="K13" t="n">
+        <v>944</v>
+      </c>
+      <c r="L13" t="n">
+        <v>109</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.104</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:23.216</t>
+          <t>2026-05-29 09:40:43.592</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779421945387</v>
+        <v>1780022441781</v>
       </c>
       <c r="C14" t="n">
-        <v>86172</v>
+        <v>85044</v>
       </c>
       <c r="D14" t="n">
-        <v>-428.6</v>
+        <v>1239.86</v>
       </c>
       <c r="E14" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F14" t="n">
-        <v>685</v>
+        <v>2319</v>
       </c>
       <c r="G14" t="n">
-        <v>48.68</v>
+        <v>279.59</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1810</v>
+      </c>
+      <c r="L14" t="n">
+        <v>113</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.055</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:23.656</t>
+          <t>2026-05-29 09:40:43.594</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779421945589</v>
+        <v>1780022441981</v>
       </c>
       <c r="C15" t="n">
-        <v>86498</v>
+        <v>86099</v>
       </c>
       <c r="D15" t="n">
-        <v>-81.17</v>
+        <v>2232.86</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F15" t="n">
-        <v>685</v>
+        <v>2319</v>
       </c>
       <c r="G15" t="n">
-        <v>48.68</v>
+        <v>279.59</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1612</v>
+      </c>
+      <c r="L15" t="n">
+        <v>107</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.203</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:23.656</t>
+          <t>2026-05-29 09:40:44.405</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779421945790</v>
+        <v>1780022442181</v>
       </c>
       <c r="C16" t="n">
-        <v>85925</v>
+        <v>85415</v>
       </c>
       <c r="D16" t="n">
-        <v>-650.11</v>
+        <v>1437.22</v>
       </c>
       <c r="E16" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>1490</v>
+        <v>2319</v>
       </c>
       <c r="G16" t="n">
-        <v>247.45</v>
+        <v>279.59</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2223</v>
+      </c>
+      <c r="L16" t="n">
+        <v>116</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.996</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:24.044</t>
+          <t>2026-05-29 09:40:44.407</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779421945991</v>
+        <v>1780022442381</v>
       </c>
       <c r="C17" t="n">
-        <v>86171</v>
+        <v>84184</v>
       </c>
       <c r="D17" t="n">
-        <v>-371.6</v>
+        <v>134.36</v>
       </c>
       <c r="E17" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F17" t="n">
-        <v>1490</v>
+        <v>2319</v>
       </c>
       <c r="G17" t="n">
-        <v>247.45</v>
+        <v>279.59</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L17" t="n">
+        <v>117</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:24.045</t>
+          <t>2026-05-29 09:40:44.418</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779421946193</v>
+        <v>1780022442581</v>
       </c>
       <c r="C18" t="n">
-        <v>86449</v>
+        <v>84155</v>
       </c>
       <c r="D18" t="n">
-        <v>-75.02</v>
+        <v>98.64</v>
       </c>
       <c r="E18" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>1490</v>
+        <v>2319</v>
       </c>
       <c r="G18" t="n">
-        <v>247.45</v>
+        <v>279.59</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1835</v>
+      </c>
+      <c r="L18" t="n">
+        <v>107</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.815</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:24.463</t>
+          <t>2026-05-29 09:40:44.425</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779421946394</v>
+        <v>1780022442781</v>
       </c>
       <c r="C19" t="n">
-        <v>86662</v>
+        <v>84886</v>
       </c>
       <c r="D19" t="n">
-        <v>141.73</v>
+        <v>824.71</v>
       </c>
       <c r="E19" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>624</v>
+        <v>2319</v>
       </c>
       <c r="G19" t="n">
-        <v>253.3</v>
+        <v>279.59</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1643</v>
+      </c>
+      <c r="L19" t="n">
+        <v>109</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:24.464</t>
+          <t>2026-05-29 09:40:44.535</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779421946596</v>
+        <v>1780022442981</v>
       </c>
       <c r="C20" t="n">
-        <v>85947</v>
+        <v>84693</v>
       </c>
       <c r="D20" t="n">
-        <v>-580.36</v>
+        <v>590.47</v>
       </c>
       <c r="E20" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F20" t="n">
-        <v>624</v>
+        <v>2319</v>
       </c>
       <c r="G20" t="n">
-        <v>253.3</v>
+        <v>279.59</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1552</v>
+      </c>
+      <c r="L20" t="n">
+        <v>113</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.666</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:24.927</t>
+          <t>2026-05-29 09:40:44.537</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779421946797</v>
+        <v>1780022443200</v>
       </c>
       <c r="C21" t="n">
-        <v>86239</v>
+        <v>84428</v>
       </c>
       <c r="D21" t="n">
-        <v>-259.34</v>
+        <v>295.95</v>
       </c>
       <c r="E21" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>624</v>
+        <v>2319</v>
       </c>
       <c r="G21" t="n">
-        <v>253.3</v>
+        <v>279.59</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1336</v>
+      </c>
+      <c r="L21" t="n">
+        <v>125</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:24.928</t>
+          <t>2026-05-29 09:40:44.538</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779421946998</v>
+        <v>1780022443400</v>
       </c>
       <c r="C22" t="n">
-        <v>86551</v>
+        <v>84405</v>
       </c>
       <c r="D22" t="n">
-        <v>65.63</v>
+        <v>258.15</v>
       </c>
       <c r="E22" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F22" t="n">
-        <v>705</v>
+        <v>2319</v>
       </c>
       <c r="G22" t="n">
-        <v>252.43</v>
+        <v>279.59</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1137</v>
+      </c>
+      <c r="L22" t="n">
+        <v>112</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:24.928</t>
+          <t>2026-05-29 09:40:44.540</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779421947200</v>
+        <v>1780022443600</v>
       </c>
       <c r="C23" t="n">
-        <v>85876</v>
+        <v>84128</v>
       </c>
       <c r="D23" t="n">
-        <v>-612.66</v>
+        <v>-31.76</v>
       </c>
       <c r="E23" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F23" t="n">
-        <v>705</v>
+        <v>2319</v>
       </c>
       <c r="G23" t="n">
-        <v>252.43</v>
+        <v>279.59</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K23" t="n">
+        <v>938</v>
+      </c>
+      <c r="L23" t="n">
+        <v>115</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.003</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:25.328</t>
+          <t>2026-05-29 09:40:44.827</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779421947401</v>
+        <v>1780022443800</v>
       </c>
       <c r="C24" t="n">
-        <v>86207</v>
+        <v>85636</v>
       </c>
       <c r="D24" t="n">
-        <v>-251.02</v>
+        <v>1477.83</v>
       </c>
       <c r="E24" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F24" t="n">
-        <v>705</v>
+        <v>2319</v>
       </c>
       <c r="G24" t="n">
-        <v>252.43</v>
+        <v>279.59</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1025</v>
+      </c>
+      <c r="L24" t="n">
+        <v>115</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:25.714</t>
+          <t>2026-05-29 09:40:45.844</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779421947603</v>
+        <v>1780022444000</v>
       </c>
       <c r="C25" t="n">
-        <v>86079</v>
+        <v>85889</v>
       </c>
       <c r="D25" t="n">
-        <v>-366.47</v>
+        <v>1656.94</v>
       </c>
       <c r="E25" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F25" t="n">
-        <v>705</v>
+        <v>5237</v>
       </c>
       <c r="G25" t="n">
-        <v>252.43</v>
+        <v>279.59</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J25" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1843</v>
+      </c>
+      <c r="L25" t="n">
+        <v>116</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.977</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:25.715</t>
+          <t>2026-05-29 09:40:45.845</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779421947804</v>
+        <v>1780022444200</v>
       </c>
       <c r="C26" t="n">
-        <v>86424</v>
+        <v>85262</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.15</v>
+        <v>947.09</v>
       </c>
       <c r="E26" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F26" t="n">
-        <v>705</v>
+        <v>5237</v>
       </c>
       <c r="G26" t="n">
-        <v>252.43</v>
+        <v>279.59</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1644</v>
+      </c>
+      <c r="L26" t="n">
+        <v>119</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:26.082</t>
+          <t>2026-05-29 09:40:45.848</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779421948005</v>
+        <v>1780022444400</v>
       </c>
       <c r="C27" t="n">
-        <v>86807</v>
+        <v>84611</v>
       </c>
       <c r="D27" t="n">
-        <v>380.01</v>
+        <v>248.74</v>
       </c>
       <c r="E27" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F27" t="n">
-        <v>927</v>
+        <v>5237</v>
       </c>
       <c r="G27" t="n">
-        <v>255.88</v>
+        <v>279.59</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1446</v>
+      </c>
+      <c r="L27" t="n">
+        <v>108</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.966</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:26.083</t>
+          <t>2026-05-29 09:40:46.144</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779421948207</v>
+        <v>1780022444600</v>
       </c>
       <c r="C28" t="n">
-        <v>87069</v>
+        <v>84950</v>
       </c>
       <c r="D28" t="n">
-        <v>623.01</v>
+        <v>575.3</v>
       </c>
       <c r="E28" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F28" t="n">
-        <v>927</v>
+        <v>5237</v>
       </c>
       <c r="G28" t="n">
-        <v>255.88</v>
+        <v>279.59</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1543</v>
+      </c>
+      <c r="L28" t="n">
+        <v>124</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:26.514</t>
+          <t>2026-05-29 09:40:46.146</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779421948408</v>
+        <v>1780022444819</v>
       </c>
       <c r="C29" t="n">
-        <v>87304</v>
+        <v>85483</v>
       </c>
       <c r="D29" t="n">
-        <v>826.86</v>
+        <v>1079.54</v>
       </c>
       <c r="E29" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F29" t="n">
-        <v>927</v>
+        <v>5237</v>
       </c>
       <c r="G29" t="n">
-        <v>255.88</v>
+        <v>279.59</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1326</v>
+      </c>
+      <c r="L29" t="n">
+        <v>108</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.108</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:26.514</t>
+          <t>2026-05-29 09:40:46.147</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779421948610</v>
+        <v>1780022445019</v>
       </c>
       <c r="C30" t="n">
-        <v>86610</v>
+        <v>85875</v>
       </c>
       <c r="D30" t="n">
-        <v>91.52</v>
+        <v>1417.56</v>
       </c>
       <c r="E30" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F30" t="n">
-        <v>927</v>
+        <v>5237</v>
       </c>
       <c r="G30" t="n">
-        <v>255.88</v>
+        <v>279.59</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1127</v>
+      </c>
+      <c r="L30" t="n">
+        <v>113</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.716</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:27.126</t>
+          <t>2026-05-29 09:40:46.148</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779421948811</v>
+        <v>1780022445219</v>
       </c>
       <c r="C31" t="n">
-        <v>86732</v>
+        <v>85624</v>
       </c>
       <c r="D31" t="n">
-        <v>208.94</v>
+        <v>1095.68</v>
       </c>
       <c r="E31" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F31" t="n">
-        <v>927</v>
+        <v>5237</v>
       </c>
       <c r="G31" t="n">
-        <v>255.88</v>
+        <v>279.59</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K31" t="n">
+        <v>928</v>
+      </c>
+      <c r="L31" t="n">
+        <v>109</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.389</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:27.143</t>
+          <t>2026-05-29 09:40:46.642</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779421949013</v>
+        <v>1780022445419</v>
       </c>
       <c r="C32" t="n">
-        <v>87185</v>
+        <v>85719</v>
       </c>
       <c r="D32" t="n">
-        <v>651.49</v>
+        <v>1135.9</v>
       </c>
       <c r="E32" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F32" t="n">
-        <v>927</v>
+        <v>5237</v>
       </c>
       <c r="G32" t="n">
-        <v>255.88</v>
+        <v>279.59</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1222</v>
+      </c>
+      <c r="L32" t="n">
+        <v>126</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.153</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:27.144</t>
+          <t>2026-05-29 09:40:46.698</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779421949214</v>
+        <v>1780022445619</v>
       </c>
       <c r="C33" t="n">
-        <v>86476</v>
+        <v>85681</v>
       </c>
       <c r="D33" t="n">
-        <v>-90.08</v>
+        <v>1041.1</v>
       </c>
       <c r="E33" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F33" t="n">
-        <v>1128</v>
+        <v>1739</v>
       </c>
       <c r="G33" t="n">
-        <v>272.94</v>
+        <v>279.59</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1078</v>
+      </c>
+      <c r="L33" t="n">
+        <v>108</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.669</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:27.543</t>
+          <t>2026-05-29 09:40:47.746</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779421949415</v>
+        <v>1780022445819</v>
       </c>
       <c r="C34" t="n">
-        <v>86977</v>
+        <v>85576</v>
       </c>
       <c r="D34" t="n">
-        <v>415.42</v>
+        <v>884.05</v>
       </c>
       <c r="E34" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F34" t="n">
-        <v>1128</v>
+        <v>1739</v>
       </c>
       <c r="G34" t="n">
-        <v>272.94</v>
+        <v>279.59</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1926</v>
+      </c>
+      <c r="L34" t="n">
+        <v>118</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.987</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:27.544</t>
+          <t>2026-05-29 09:40:47.749</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779421949617</v>
+        <v>1780022446019</v>
       </c>
       <c r="C35" t="n">
-        <v>87411</v>
+        <v>85585</v>
       </c>
       <c r="D35" t="n">
-        <v>828.65</v>
+        <v>848.85</v>
       </c>
       <c r="E35" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F35" t="n">
-        <v>503</v>
+        <v>1739</v>
       </c>
       <c r="G35" t="n">
-        <v>293.38</v>
+        <v>279.59</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1729</v>
+      </c>
+      <c r="L35" t="n">
+        <v>109</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.186</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:27.926</t>
+          <t>2026-05-29 09:40:47.751</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779421949818</v>
+        <v>1780022446219</v>
       </c>
       <c r="C36" t="n">
-        <v>86715</v>
+        <v>85210</v>
       </c>
       <c r="D36" t="n">
-        <v>91.22</v>
+        <v>431.4</v>
       </c>
       <c r="E36" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F36" t="n">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G36" t="n">
-        <v>293.38</v>
+        <v>287.98</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1531</v>
+      </c>
+      <c r="L36" t="n">
+        <v>109</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.755</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:27.926</t>
+          <t>2026-05-29 09:40:47.753</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779421950020</v>
+        <v>1780022446438</v>
       </c>
       <c r="C37" t="n">
-        <v>87153</v>
+        <v>84424</v>
       </c>
       <c r="D37" t="n">
-        <v>524.66</v>
+        <v>-376.17</v>
       </c>
       <c r="E37" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F37" t="n">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G37" t="n">
-        <v>293.38</v>
+        <v>287.98</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1314</v>
+      </c>
+      <c r="L37" t="n">
+        <v>112</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.264</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:28.360</t>
+          <t>2026-05-29 09:40:47.766</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779421950221</v>
+        <v>1780022446638</v>
       </c>
       <c r="C38" t="n">
-        <v>87563</v>
+        <v>84349</v>
       </c>
       <c r="D38" t="n">
-        <v>908.42</v>
+        <v>-432.36</v>
       </c>
       <c r="E38" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F38" t="n">
-        <v>584</v>
+        <v>500</v>
       </c>
       <c r="G38" t="n">
-        <v>298.01</v>
+        <v>287.98</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1127</v>
+      </c>
+      <c r="L38" t="n">
+        <v>113</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.878</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:28.361</t>
+          <t>2026-05-29 09:40:47.919</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779421950422</v>
+        <v>1780022446838</v>
       </c>
       <c r="C39" t="n">
-        <v>86771</v>
+        <v>84373</v>
       </c>
       <c r="D39" t="n">
-        <v>71</v>
+        <v>-386.74</v>
       </c>
       <c r="E39" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F39" t="n">
-        <v>584</v>
+        <v>500</v>
       </c>
       <c r="G39" t="n">
-        <v>298.01</v>
+        <v>287.98</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1079</v>
+      </c>
+      <c r="L39" t="n">
+        <v>105</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.708</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:28.362</t>
+          <t>2026-05-29 09:40:48.505</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779421950624</v>
+        <v>1780022447038</v>
       </c>
       <c r="C40" t="n">
-        <v>87146</v>
+        <v>84770</v>
       </c>
       <c r="D40" t="n">
-        <v>442.45</v>
+        <v>29.6</v>
       </c>
       <c r="E40" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F40" t="n">
-        <v>584</v>
+        <v>500</v>
       </c>
       <c r="G40" t="n">
-        <v>298.01</v>
+        <v>287.98</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1466</v>
+      </c>
+      <c r="L40" t="n">
+        <v>112</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.926</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:29.166</t>
+          <t>2026-05-29 09:40:48.506</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779421950825</v>
+        <v>1780022447238</v>
       </c>
       <c r="C41" t="n">
-        <v>87480</v>
+        <v>84767</v>
       </c>
       <c r="D41" t="n">
-        <v>754.33</v>
+        <v>25.12</v>
       </c>
       <c r="E41" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F41" t="n">
-        <v>685</v>
+        <v>1079</v>
       </c>
       <c r="G41" t="n">
-        <v>300.8</v>
+        <v>307.35</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1267</v>
+      </c>
+      <c r="L41" t="n">
+        <v>109</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.994</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:29.167</t>
+          <t>2026-05-29 09:40:49.778</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779421951027</v>
+        <v>1780022447438</v>
       </c>
       <c r="C42" t="n">
-        <v>86709</v>
+        <v>84845</v>
       </c>
       <c r="D42" t="n">
-        <v>-54.39</v>
+        <v>101.86</v>
       </c>
       <c r="E42" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F42" t="n">
-        <v>685</v>
+        <v>1079</v>
       </c>
       <c r="G42" t="n">
-        <v>300.8</v>
+        <v>307.35</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2339</v>
+      </c>
+      <c r="L42" t="n">
+        <v>117</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.295</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:29.168</t>
+          <t>2026-05-29 09:40:49.780</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779421951228</v>
+        <v>1780022447638</v>
       </c>
       <c r="C43" t="n">
-        <v>87140</v>
+        <v>84567</v>
       </c>
       <c r="D43" t="n">
-        <v>379.33</v>
+        <v>-181.23</v>
       </c>
       <c r="E43" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F43" t="n">
-        <v>685</v>
+        <v>1079</v>
       </c>
       <c r="G43" t="n">
-        <v>300.8</v>
+        <v>307.35</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2141</v>
+      </c>
+      <c r="L43" t="n">
+        <v>108</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.914</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:29.168</t>
+          <t>2026-05-29 09:40:49.781</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779421951429</v>
+        <v>1780022447838</v>
       </c>
       <c r="C44" t="n">
-        <v>87523</v>
+        <v>84661</v>
       </c>
       <c r="D44" t="n">
-        <v>743.37</v>
+        <v>-78.17</v>
       </c>
       <c r="E44" t="n">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F44" t="n">
-        <v>624</v>
+        <v>1079</v>
       </c>
       <c r="G44" t="n">
-        <v>304.03</v>
+        <v>307.35</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1942</v>
+      </c>
+      <c r="L44" t="n">
+        <v>106</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.965</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:29.579</t>
+          <t>2026-05-29 09:40:49.782</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779421951631</v>
+        <v>1780022448038</v>
       </c>
       <c r="C45" t="n">
-        <v>87390</v>
+        <v>84750</v>
       </c>
       <c r="D45" t="n">
-        <v>573.2</v>
+        <v>14.74</v>
       </c>
       <c r="E45" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="F45" t="n">
-        <v>624</v>
+        <v>840</v>
       </c>
       <c r="G45" t="n">
-        <v>304.03</v>
+        <v>296.35</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1743</v>
+      </c>
+      <c r="L45" t="n">
+        <v>105</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:29.607</t>
+          <t>2026-05-29 09:40:50.402</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779421951832</v>
+        <v>1780022448257</v>
       </c>
       <c r="C46" t="n">
-        <v>87302</v>
+        <v>84916</v>
       </c>
       <c r="D46" t="n">
-        <v>456.54</v>
+        <v>180</v>
       </c>
       <c r="E46" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="F46" t="n">
-        <v>624</v>
+        <v>840</v>
       </c>
       <c r="G46" t="n">
-        <v>304.03</v>
+        <v>296.35</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2143</v>
+      </c>
+      <c r="L46" t="n">
+        <v>107</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.715</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:29.981</t>
+          <t>2026-05-29 09:40:50.542</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779421952034</v>
+        <v>1780022448457</v>
       </c>
       <c r="C47" t="n">
-        <v>87608</v>
+        <v>85136</v>
       </c>
       <c r="D47" t="n">
-        <v>739.71</v>
+        <v>391</v>
       </c>
       <c r="E47" t="n">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="F47" t="n">
-        <v>624</v>
+        <v>840</v>
       </c>
       <c r="G47" t="n">
-        <v>304.03</v>
+        <v>296.35</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J47" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2084</v>
+      </c>
+      <c r="L47" t="n">
+        <v>117</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.877</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:29.993</t>
+          <t>2026-05-29 09:40:50.603</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779421952235</v>
+        <v>1780022448657</v>
       </c>
       <c r="C48" t="n">
-        <v>87943</v>
+        <v>85159</v>
       </c>
       <c r="D48" t="n">
-        <v>1037.73</v>
+        <v>394.45</v>
       </c>
       <c r="E48" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F48" t="n">
-        <v>665</v>
+        <v>840</v>
       </c>
       <c r="G48" t="n">
-        <v>304.9</v>
+        <v>296.35</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J48" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1945</v>
+      </c>
+      <c r="L48" t="n">
+        <v>112</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:30.538</t>
+          <t>2026-05-29 09:40:50.953</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779421952436</v>
+        <v>1780022448857</v>
       </c>
       <c r="C49" t="n">
-        <v>87118</v>
+        <v>84971</v>
       </c>
       <c r="D49" t="n">
-        <v>160.84</v>
+        <v>186.73</v>
       </c>
       <c r="E49" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F49" t="n">
-        <v>665</v>
+        <v>840</v>
       </c>
       <c r="G49" t="n">
-        <v>304.9</v>
+        <v>296.35</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J49" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K49" t="n">
+        <v>2094</v>
+      </c>
+      <c r="L49" t="n">
+        <v>106</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.891</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:30.539</t>
+          <t>2026-05-29 09:40:51.023</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779421952638</v>
+        <v>1780022449657</v>
       </c>
       <c r="C50" t="n">
-        <v>87519</v>
+        <v>84997</v>
       </c>
       <c r="D50" t="n">
-        <v>553.8</v>
+        <v>203.39</v>
       </c>
       <c r="E50" t="n">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F50" t="n">
-        <v>665</v>
+        <v>840</v>
       </c>
       <c r="G50" t="n">
-        <v>304.9</v>
+        <v>296.35</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>59.63</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1363</v>
+      </c>
+      <c r="L50" t="n">
+        <v>115</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.206</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:30.901</t>
+          <t>2026-05-29 09:40:51.037</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779421952839</v>
+        <v>1780022449876</v>
       </c>
       <c r="C51" t="n">
-        <v>87878</v>
+        <v>85951</v>
       </c>
       <c r="D51" t="n">
-        <v>885.11</v>
+        <v>1147.22</v>
       </c>
       <c r="E51" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F51" t="n">
-        <v>705</v>
+        <v>840</v>
       </c>
       <c r="G51" t="n">
-        <v>181.9</v>
+        <v>296.35</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L51" t="n">
+        <v>115</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:30.901</t>
+          <t>2026-05-29 09:40:51.642</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779421953041</v>
+        <v>1780022450076</v>
       </c>
       <c r="C52" t="n">
-        <v>86992</v>
+        <v>86041</v>
       </c>
       <c r="D52" t="n">
-        <v>-45.15</v>
+        <v>1179.86</v>
       </c>
       <c r="E52" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F52" t="n">
-        <v>705</v>
+        <v>840</v>
       </c>
       <c r="G52" t="n">
-        <v>181.9</v>
+        <v>296.35</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1564</v>
+      </c>
+      <c r="L52" t="n">
+        <v>113</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2.312</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:31.242</t>
+          <t>2026-05-29 09:40:51.657</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779421953242</v>
+        <v>1780022450276</v>
       </c>
       <c r="C53" t="n">
-        <v>87417</v>
+        <v>85886</v>
       </c>
       <c r="D53" t="n">
-        <v>382.11</v>
+        <v>965.87</v>
       </c>
       <c r="E53" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F53" t="n">
-        <v>705</v>
+        <v>840</v>
       </c>
       <c r="G53" t="n">
-        <v>181.9</v>
+        <v>296.35</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1379</v>
+      </c>
+      <c r="L53" t="n">
+        <v>114</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.456</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:31.243</t>
+          <t>2026-05-29 09:40:51.685</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779421953443</v>
+        <v>1780022450476</v>
       </c>
       <c r="C54" t="n">
-        <v>87843</v>
+        <v>85717</v>
       </c>
       <c r="D54" t="n">
-        <v>789</v>
+        <v>748.5700000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F54" t="n">
-        <v>705</v>
+        <v>840</v>
       </c>
       <c r="G54" t="n">
-        <v>181.9</v>
+        <v>296.35</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1207</v>
+      </c>
+      <c r="L54" t="n">
+        <v>109</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.116</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:31.647</t>
+          <t>2026-05-29 09:40:52.812</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779421953645</v>
+        <v>1780022450676</v>
       </c>
       <c r="C55" t="n">
-        <v>87715</v>
+        <v>85517</v>
       </c>
       <c r="D55" t="n">
-        <v>621.55</v>
+        <v>511.15</v>
       </c>
       <c r="E55" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F55" t="n">
-        <v>665</v>
+        <v>840</v>
       </c>
       <c r="G55" t="n">
-        <v>180.07</v>
+        <v>296.35</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2134</v>
+      </c>
+      <c r="L55" t="n">
+        <v>119</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.07</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:31.648</t>
+          <t>2026-05-29 09:40:52.814</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779421953846</v>
+        <v>1780022450876</v>
       </c>
       <c r="C56" t="n">
-        <v>87293</v>
+        <v>85719</v>
       </c>
       <c r="D56" t="n">
-        <v>168.48</v>
+        <v>687.59</v>
       </c>
       <c r="E56" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F56" t="n">
-        <v>665</v>
+        <v>840</v>
       </c>
       <c r="G56" t="n">
-        <v>180.07</v>
+        <v>296.35</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1937</v>
+      </c>
+      <c r="L56" t="n">
+        <v>108</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.249</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:32.041</t>
+          <t>2026-05-29 09:40:52.840</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779421954048</v>
+        <v>1780022451076</v>
       </c>
       <c r="C57" t="n">
-        <v>87523</v>
+        <v>85729</v>
       </c>
       <c r="D57" t="n">
-        <v>390.05</v>
+        <v>663.21</v>
       </c>
       <c r="E57" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F57" t="n">
-        <v>665</v>
+        <v>840</v>
       </c>
       <c r="G57" t="n">
-        <v>180.07</v>
+        <v>296.35</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1762</v>
+      </c>
+      <c r="L57" t="n">
+        <v>104</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:32.042</t>
+          <t>2026-05-29 09:40:53.135</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779421954249</v>
+        <v>1780022451276</v>
       </c>
       <c r="C58" t="n">
-        <v>87926</v>
+        <v>85579</v>
       </c>
       <c r="D58" t="n">
-        <v>773.55</v>
+        <v>480.05</v>
       </c>
       <c r="E58" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F58" t="n">
-        <v>765</v>
+        <v>840</v>
       </c>
       <c r="G58" t="n">
-        <v>180.55</v>
+        <v>296.35</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1857</v>
+      </c>
+      <c r="L58" t="n">
+        <v>111</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.353</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:32.638</t>
+          <t>2026-05-29 09:40:53.176</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779421954450</v>
+        <v>1780022451476</v>
       </c>
       <c r="C59" t="n">
-        <v>87086</v>
+        <v>85513</v>
       </c>
       <c r="D59" t="n">
-        <v>-105.13</v>
+        <v>390.05</v>
       </c>
       <c r="E59" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F59" t="n">
-        <v>765</v>
+        <v>840</v>
       </c>
       <c r="G59" t="n">
-        <v>180.55</v>
+        <v>296.35</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1699</v>
+      </c>
+      <c r="L59" t="n">
+        <v>109</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.511</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:32.639</t>
+          <t>2026-05-29 09:40:53.191</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779421954652</v>
+        <v>1780022451695</v>
       </c>
       <c r="C60" t="n">
-        <v>87393</v>
+        <v>85090</v>
       </c>
       <c r="D60" t="n">
-        <v>207.13</v>
+        <v>-52.46</v>
       </c>
       <c r="E60" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F60" t="n">
-        <v>765</v>
+        <v>840</v>
       </c>
       <c r="G60" t="n">
-        <v>180.55</v>
+        <v>296.35</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1494</v>
+      </c>
+      <c r="L60" t="n">
+        <v>106</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2.231</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:32.639</t>
+          <t>2026-05-29 09:40:53.259</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779421954853</v>
+        <v>1780022451895</v>
       </c>
       <c r="C61" t="n">
-        <v>87639</v>
+        <v>85105</v>
       </c>
       <c r="D61" t="n">
-        <v>442.77</v>
+        <v>-34.83</v>
       </c>
       <c r="E61" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F61" t="n">
-        <v>765</v>
+        <v>840</v>
       </c>
       <c r="G61" t="n">
-        <v>180.55</v>
+        <v>296.35</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1363</v>
+      </c>
+      <c r="L61" t="n">
+        <v>108</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.969</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:33.086</t>
+          <t>2026-05-29 09:40:53.264</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779421955055</v>
+        <v>1780022452095</v>
       </c>
       <c r="C62" t="n">
-        <v>87938</v>
+        <v>85504</v>
       </c>
       <c r="D62" t="n">
-        <v>719.63</v>
+        <v>365.91</v>
       </c>
       <c r="E62" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F62" t="n">
-        <v>725</v>
+        <v>840</v>
       </c>
       <c r="G62" t="n">
-        <v>166.18</v>
+        <v>296.35</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1168</v>
+      </c>
+      <c r="L62" t="n">
+        <v>105</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.301</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:33.087</t>
+          <t>2026-05-29 09:40:53.414</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779421955256</v>
+        <v>1780022452295</v>
       </c>
       <c r="C63" t="n">
-        <v>87112</v>
+        <v>85384</v>
       </c>
       <c r="D63" t="n">
-        <v>-142.35</v>
+        <v>227.61</v>
       </c>
       <c r="E63" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F63" t="n">
-        <v>725</v>
+        <v>4157</v>
       </c>
       <c r="G63" t="n">
-        <v>166.18</v>
+        <v>296.35</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J63" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1118</v>
+      </c>
+      <c r="L63" t="n">
+        <v>120</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.291</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:33.896</t>
+          <t>2026-05-29 09:40:53.937</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779421955457</v>
+        <v>1780022452496</v>
       </c>
       <c r="C64" t="n">
-        <v>87415</v>
+        <v>85268</v>
       </c>
       <c r="D64" t="n">
-        <v>167.77</v>
+        <v>100.23</v>
       </c>
       <c r="E64" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F64" t="n">
-        <v>725</v>
+        <v>4157</v>
       </c>
       <c r="G64" t="n">
-        <v>166.18</v>
+        <v>296.35</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J64" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1440</v>
+      </c>
+      <c r="L64" t="n">
+        <v>140</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.092</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:33.896</t>
+          <t>2026-05-29 09:40:53.939</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779421955659</v>
+        <v>1780022452695</v>
       </c>
       <c r="C65" t="n">
-        <v>87715</v>
+        <v>85268</v>
       </c>
       <c r="D65" t="n">
-        <v>459.38</v>
+        <v>95.22</v>
       </c>
       <c r="E65" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F65" t="n">
-        <v>725</v>
+        <v>4157</v>
       </c>
       <c r="G65" t="n">
-        <v>166.18</v>
+        <v>296.35</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1243</v>
+      </c>
+      <c r="L65" t="n">
+        <v>107</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:33.897</t>
+          <t>2026-05-29 09:40:53.940</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779421955860</v>
+        <v>1780022452895</v>
       </c>
       <c r="C66" t="n">
-        <v>87328</v>
+        <v>85196</v>
       </c>
       <c r="D66" t="n">
-        <v>49.41</v>
+        <v>18.46</v>
       </c>
       <c r="E66" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F66" t="n">
-        <v>745</v>
+        <v>4157</v>
       </c>
       <c r="G66" t="n">
-        <v>79.2</v>
+        <v>296.35</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1044</v>
+      </c>
+      <c r="L66" t="n">
+        <v>96</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.101</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:33.897</t>
+          <t>2026-05-29 09:40:55.065</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779421956062</v>
+        <v>1780022453095</v>
       </c>
       <c r="C67" t="n">
-        <v>87442</v>
+        <v>85375</v>
       </c>
       <c r="D67" t="n">
-        <v>160.94</v>
+        <v>196.54</v>
       </c>
       <c r="E67" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F67" t="n">
-        <v>745</v>
+        <v>4157</v>
       </c>
       <c r="G67" t="n">
-        <v>79.2</v>
+        <v>296.35</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1968</v>
+      </c>
+      <c r="L67" t="n">
+        <v>123</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2.294</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:34.314</t>
+          <t>2026-05-29 09:40:55.142</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779421956263</v>
+        <v>1780022453295</v>
       </c>
       <c r="C68" t="n">
-        <v>87740</v>
+        <v>85481</v>
       </c>
       <c r="D68" t="n">
-        <v>450.89</v>
+        <v>292.71</v>
       </c>
       <c r="E68" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F68" t="n">
-        <v>745</v>
+        <v>1060</v>
       </c>
       <c r="G68" t="n">
-        <v>79.2</v>
+        <v>282</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1845</v>
+      </c>
+      <c r="L68" t="n">
+        <v>123</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.819</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:34.347</t>
+          <t>2026-05-29 09:40:55.144</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779421956464</v>
+        <v>1780022453514</v>
       </c>
       <c r="C69" t="n">
-        <v>88124</v>
+        <v>85520</v>
       </c>
       <c r="D69" t="n">
-        <v>812.35</v>
+        <v>317.07</v>
       </c>
       <c r="E69" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F69" t="n">
-        <v>624</v>
+        <v>1060</v>
       </c>
       <c r="G69" t="n">
-        <v>57.78</v>
+        <v>282</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1629</v>
+      </c>
+      <c r="L69" t="n">
+        <v>113</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:34.685</t>
+          <t>2026-05-29 09:40:55.145</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779421956666</v>
+        <v>1780022453714</v>
       </c>
       <c r="C70" t="n">
-        <v>87267</v>
+        <v>85396</v>
       </c>
       <c r="D70" t="n">
-        <v>-85.27</v>
+        <v>177.22</v>
       </c>
       <c r="E70" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F70" t="n">
-        <v>624</v>
+        <v>1060</v>
       </c>
       <c r="G70" t="n">
-        <v>57.78</v>
+        <v>282</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1430</v>
+      </c>
+      <c r="L70" t="n">
+        <v>92</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.676</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:34.685</t>
+          <t>2026-05-29 09:40:57.852</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779421956867</v>
+        <v>1780022453914</v>
       </c>
       <c r="C71" t="n">
-        <v>87613</v>
+        <v>85531</v>
       </c>
       <c r="D71" t="n">
-        <v>265</v>
+        <v>303.36</v>
       </c>
       <c r="E71" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F71" t="n">
-        <v>624</v>
+        <v>1060</v>
       </c>
       <c r="G71" t="n">
-        <v>57.78</v>
+        <v>282</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3936</v>
+      </c>
+      <c r="L71" t="n">
+        <v>107</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.379</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:35.512</t>
+          <t>2026-05-29 09:40:57.853</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779421957069</v>
+        <v>1780022454114</v>
       </c>
       <c r="C72" t="n">
-        <v>87951</v>
+        <v>85682</v>
       </c>
       <c r="D72" t="n">
-        <v>589.75</v>
+        <v>439.19</v>
       </c>
       <c r="E72" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F72" t="n">
-        <v>705</v>
+        <v>779</v>
       </c>
       <c r="G72" t="n">
-        <v>47.5</v>
+        <v>282.24</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J72" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3738</v>
+      </c>
+      <c r="L72" t="n">
+        <v>109</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.724</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:35.513</t>
+          <t>2026-05-29 09:40:57.855</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779421957270</v>
+        <v>1780022454314</v>
       </c>
       <c r="C73" t="n">
-        <v>87263</v>
+        <v>85759</v>
       </c>
       <c r="D73" t="n">
-        <v>-127.74</v>
+        <v>494.23</v>
       </c>
       <c r="E73" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F73" t="n">
-        <v>705</v>
+        <v>779</v>
       </c>
       <c r="G73" t="n">
-        <v>47.5</v>
+        <v>282.24</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J73" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K73" t="n">
+        <v>3539</v>
+      </c>
+      <c r="L73" t="n">
+        <v>104</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.707</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:35.513</t>
+          <t>2026-05-29 09:40:57.856</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779421957471</v>
+        <v>1780022456413</v>
       </c>
       <c r="C74" t="n">
-        <v>87405</v>
+        <v>85261</v>
       </c>
       <c r="D74" t="n">
-        <v>20.65</v>
+        <v>-28.48</v>
       </c>
       <c r="E74" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F74" t="n">
-        <v>705</v>
+        <v>779</v>
       </c>
       <c r="G74" t="n">
-        <v>47.5</v>
+        <v>282.24</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1442</v>
+      </c>
+      <c r="L74" t="n">
+        <v>108</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.864</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:35.514</t>
+          <t>2026-05-29 09:40:57.857</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779421957673</v>
+        <v>1780022456632</v>
       </c>
       <c r="C75" t="n">
-        <v>87700</v>
+        <v>84771</v>
       </c>
       <c r="D75" t="n">
-        <v>314.61</v>
+        <v>-517.0599999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F75" t="n">
-        <v>705</v>
+        <v>779</v>
       </c>
       <c r="G75" t="n">
-        <v>47.5</v>
+        <v>282.24</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1224</v>
+      </c>
+      <c r="L75" t="n">
+        <v>117</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.086</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:35.931</t>
+          <t>2026-05-29 09:40:57.858</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779421957874</v>
+        <v>1780022456832</v>
       </c>
       <c r="C76" t="n">
-        <v>88004</v>
+        <v>84710</v>
       </c>
       <c r="D76" t="n">
-        <v>602.88</v>
+        <v>-552.2</v>
       </c>
       <c r="E76" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F76" t="n">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="G76" t="n">
-        <v>53.13</v>
+        <v>282.24</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1025</v>
+      </c>
+      <c r="L76" t="n">
+        <v>101</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.017</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:35.955</t>
+          <t>2026-05-29 09:40:58.204</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779421958076</v>
+        <v>1780022457032</v>
       </c>
       <c r="C77" t="n">
-        <v>87134</v>
+        <v>84649</v>
       </c>
       <c r="D77" t="n">
-        <v>-297.26</v>
+        <v>-585.59</v>
       </c>
       <c r="E77" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F77" t="n">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="G77" t="n">
-        <v>53.13</v>
+        <v>282.24</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1170</v>
+      </c>
+      <c r="L77" t="n">
+        <v>104</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.521</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:36.563</t>
+          <t>2026-05-29 09:40:58.206</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779421958277</v>
+        <v>1780022457232</v>
       </c>
       <c r="C78" t="n">
-        <v>87425</v>
+        <v>84704</v>
       </c>
       <c r="D78" t="n">
-        <v>8.6</v>
+        <v>-501.31</v>
       </c>
       <c r="E78" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F78" t="n">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="G78" t="n">
-        <v>53.13</v>
+        <v>282.24</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J78" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K78" t="n">
+        <v>972</v>
+      </c>
+      <c r="L78" t="n">
+        <v>115</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.113</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:36.580</t>
+          <t>2026-05-29 09:40:58.815</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779421958479</v>
+        <v>1780022457432</v>
       </c>
       <c r="C79" t="n">
-        <v>87754</v>
+        <v>84794</v>
       </c>
       <c r="D79" t="n">
-        <v>337.17</v>
+        <v>-386.25</v>
       </c>
       <c r="E79" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F79" t="n">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="G79" t="n">
-        <v>53.13</v>
+        <v>282.24</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1382</v>
+      </c>
+      <c r="L79" t="n">
+        <v>112</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.109</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:36.581</t>
+          <t>2026-05-29 09:40:58.817</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779421958680</v>
+        <v>1780022457632</v>
       </c>
       <c r="C80" t="n">
-        <v>87180</v>
+        <v>84877</v>
       </c>
       <c r="D80" t="n">
-        <v>-253.69</v>
+        <v>-283.93</v>
       </c>
       <c r="E80" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F80" t="n">
-        <v>724</v>
+        <v>3578</v>
       </c>
       <c r="G80" t="n">
-        <v>46.44</v>
+        <v>282.24</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1183</v>
+      </c>
+      <c r="L80" t="n">
+        <v>119</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.162</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:36.937</t>
+          <t>2026-05-29 09:40:58.943</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779421958881</v>
+        <v>1780022457833</v>
       </c>
       <c r="C81" t="n">
-        <v>87395</v>
+        <v>85035</v>
       </c>
       <c r="D81" t="n">
-        <v>-26</v>
+        <v>-111.74</v>
       </c>
       <c r="E81" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F81" t="n">
-        <v>724</v>
+        <v>3578</v>
       </c>
       <c r="G81" t="n">
-        <v>46.44</v>
+        <v>282.24</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1109</v>
+      </c>
+      <c r="L81" t="n">
+        <v>108</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:36.938</t>
+          <t>2026-05-29 09:40:59.272</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779421959083</v>
+        <v>1780022458032</v>
       </c>
       <c r="C82" t="n">
-        <v>87547</v>
+        <v>84939</v>
       </c>
       <c r="D82" t="n">
-        <v>127.3</v>
+        <v>-202.15</v>
       </c>
       <c r="E82" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F82" t="n">
-        <v>724</v>
+        <v>3578</v>
       </c>
       <c r="G82" t="n">
-        <v>46.44</v>
+        <v>282.24</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1240</v>
+      </c>
+      <c r="L82" t="n">
+        <v>113</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:37.365</t>
+          <t>2026-05-29 09:40:59.490</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779421959284</v>
+        <v>1780022458252</v>
       </c>
       <c r="C83" t="n">
-        <v>87178</v>
+        <v>84622</v>
       </c>
       <c r="D83" t="n">
-        <v>-248.07</v>
+        <v>-509.04</v>
       </c>
       <c r="E83" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F83" t="n">
-        <v>664</v>
+        <v>3578</v>
       </c>
       <c r="G83" t="n">
-        <v>46.54</v>
+        <v>282.24</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1237</v>
+      </c>
+      <c r="L83" t="n">
+        <v>107</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.085</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:37.366</t>
+          <t>2026-05-29 09:40:59.491</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779421959486</v>
+        <v>1780022458452</v>
       </c>
       <c r="C84" t="n">
-        <v>87101</v>
+        <v>84431</v>
       </c>
       <c r="D84" t="n">
-        <v>-312.66</v>
+        <v>-674.59</v>
       </c>
       <c r="E84" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F84" t="n">
-        <v>664</v>
+        <v>3578</v>
       </c>
       <c r="G84" t="n">
-        <v>46.54</v>
+        <v>282.24</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1038</v>
+      </c>
+      <c r="L84" t="n">
+        <v>106</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.228</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:37.770</t>
+          <t>2026-05-29 09:40:59.493</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779421959687</v>
+        <v>1780022458651</v>
       </c>
       <c r="C85" t="n">
-        <v>87296</v>
+        <v>84145</v>
       </c>
       <c r="D85" t="n">
-        <v>-102.03</v>
+        <v>-926.86</v>
       </c>
       <c r="E85" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F85" t="n">
-        <v>664</v>
+        <v>3578</v>
       </c>
       <c r="G85" t="n">
-        <v>46.54</v>
+        <v>282.24</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K85" t="n">
+        <v>841</v>
+      </c>
+      <c r="L85" t="n">
+        <v>120</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.931</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:37.775</t>
+          <t>2026-05-29 09:40:59.844</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779421959888</v>
+        <v>1780022458851</v>
       </c>
       <c r="C86" t="n">
-        <v>87598</v>
+        <v>84716</v>
       </c>
       <c r="D86" t="n">
-        <v>205.07</v>
+        <v>-309.52</v>
       </c>
       <c r="E86" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="F86" t="n">
-        <v>665</v>
+        <v>3578</v>
       </c>
       <c r="G86" t="n">
-        <v>48.59</v>
+        <v>282.24</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K86" t="n">
+        <v>991</v>
+      </c>
+      <c r="L86" t="n">
+        <v>113</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.135</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:38.446</t>
+          <t>2026-05-29 09:41:00.397</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779421960090</v>
+        <v>1780022459053</v>
       </c>
       <c r="C87" t="n">
-        <v>86851</v>
+        <v>84227</v>
       </c>
       <c r="D87" t="n">
-        <v>-552.1799999999999</v>
+        <v>-783.04</v>
       </c>
       <c r="E87" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F87" t="n">
-        <v>665</v>
+        <v>1399</v>
       </c>
       <c r="G87" t="n">
-        <v>48.59</v>
+        <v>321.62</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>52.01</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1342</v>
+      </c>
+      <c r="L87" t="n">
+        <v>107</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.385</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:38.447</t>
+          <t>2026-05-29 09:41:00.399</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779421960291</v>
+        <v>1780022459271</v>
       </c>
       <c r="C88" t="n">
-        <v>87227</v>
+        <v>83930</v>
       </c>
       <c r="D88" t="n">
-        <v>-148.57</v>
+        <v>-1040.89</v>
       </c>
       <c r="E88" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="F88" t="n">
-        <v>665</v>
+        <v>1399</v>
       </c>
       <c r="G88" t="n">
-        <v>48.59</v>
+        <v>321.62</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1127</v>
+      </c>
+      <c r="L88" t="n">
+        <v>121</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.929</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:38.447</t>
+          <t>2026-05-29 09:41:00.400</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779421960493</v>
+        <v>1780022459471</v>
       </c>
       <c r="C89" t="n">
-        <v>87575</v>
+        <v>83994</v>
       </c>
       <c r="D89" t="n">
-        <v>206.85</v>
+        <v>-924.85</v>
       </c>
       <c r="E89" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F89" t="n">
-        <v>604</v>
+        <v>1399</v>
       </c>
       <c r="G89" t="n">
-        <v>57.22</v>
+        <v>321.62</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K89" t="n">
+        <v>928</v>
+      </c>
+      <c r="L89" t="n">
+        <v>109</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.102</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:38.802</t>
+          <t>2026-05-29 09:41:01.170</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779421960694</v>
+        <v>1780022459671</v>
       </c>
       <c r="C90" t="n">
-        <v>86753</v>
+        <v>84177</v>
       </c>
       <c r="D90" t="n">
-        <v>-625.49</v>
+        <v>-695.6</v>
       </c>
       <c r="E90" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F90" t="n">
-        <v>604</v>
+        <v>1399</v>
       </c>
       <c r="G90" t="n">
-        <v>57.22</v>
+        <v>321.62</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1497</v>
+      </c>
+      <c r="L90" t="n">
+        <v>110</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.504</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:38.803</t>
+          <t>2026-05-29 09:41:01.198</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779421960895</v>
+        <v>1780022459890</v>
       </c>
       <c r="C91" t="n">
-        <v>87118</v>
+        <v>84321</v>
       </c>
       <c r="D91" t="n">
-        <v>-229.21</v>
+        <v>-516.8200000000001</v>
       </c>
       <c r="E91" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="F91" t="n">
-        <v>604</v>
+        <v>819</v>
       </c>
       <c r="G91" t="n">
-        <v>57.22</v>
+        <v>312.26</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1306</v>
+      </c>
+      <c r="L91" t="n">
+        <v>108</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.284</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:39.269</t>
+          <t>2026-05-29 09:41:01.595</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779421961097</v>
+        <v>1780022460090</v>
       </c>
       <c r="C92" t="n">
-        <v>87383</v>
+        <v>84064</v>
       </c>
       <c r="D92" t="n">
-        <v>47.25</v>
+        <v>-747.98</v>
       </c>
       <c r="E92" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="F92" t="n">
-        <v>604</v>
+        <v>819</v>
       </c>
       <c r="G92" t="n">
-        <v>57.22</v>
+        <v>312.26</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1503</v>
+      </c>
+      <c r="L92" t="n">
+        <v>115</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1.267</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:39.294</t>
+          <t>2026-05-29 09:41:01.597</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779421961298</v>
+        <v>1780022460290</v>
       </c>
       <c r="C93" t="n">
-        <v>86962</v>
+        <v>84527</v>
       </c>
       <c r="D93" t="n">
-        <v>-376.12</v>
+        <v>-247.58</v>
       </c>
       <c r="E93" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="F93" t="n">
-        <v>665</v>
+        <v>819</v>
       </c>
       <c r="G93" t="n">
-        <v>52.94</v>
+        <v>312.26</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1305</v>
+      </c>
+      <c r="L93" t="n">
+        <v>105</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:39.934</t>
+          <t>2026-05-29 09:41:01.598</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779421961500</v>
+        <v>1780022460490</v>
       </c>
       <c r="C94" t="n">
-        <v>86879</v>
+        <v>84929</v>
       </c>
       <c r="D94" t="n">
-        <v>-440.31</v>
+        <v>166.8</v>
       </c>
       <c r="E94" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F94" t="n">
-        <v>665</v>
+        <v>540</v>
       </c>
       <c r="G94" t="n">
-        <v>52.94</v>
+        <v>332.36</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1107</v>
+      </c>
+      <c r="L94" t="n">
+        <v>103</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.058</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:39.943</t>
+          <t>2026-05-29 09:41:01.599</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779421961701</v>
+        <v>1780022460690</v>
       </c>
       <c r="C95" t="n">
-        <v>87082</v>
+        <v>84562</v>
       </c>
       <c r="D95" t="n">
-        <v>-215.29</v>
+        <v>-208.54</v>
       </c>
       <c r="E95" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F95" t="n">
-        <v>665</v>
+        <v>540</v>
       </c>
       <c r="G95" t="n">
-        <v>52.94</v>
+        <v>332.36</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>909</v>
+      </c>
+      <c r="L95" t="n">
+        <v>105</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.724</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:39.943</t>
+          <t>2026-05-29 09:41:02.165</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779421961903</v>
+        <v>1780022460890</v>
       </c>
       <c r="C96" t="n">
-        <v>87308</v>
+        <v>84892</v>
       </c>
       <c r="D96" t="n">
-        <v>21.47</v>
+        <v>131.88</v>
       </c>
       <c r="E96" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F96" t="n">
-        <v>745</v>
+        <v>540</v>
       </c>
       <c r="G96" t="n">
-        <v>54.8</v>
+        <v>332.36</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1273</v>
+      </c>
+      <c r="L96" t="n">
+        <v>109</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.579</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:39.988</t>
+          <t>2026-05-29 09:41:02.202</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779421962104</v>
+        <v>1780022461090</v>
       </c>
       <c r="C97" t="n">
-        <v>86519</v>
+        <v>84399</v>
       </c>
       <c r="D97" t="n">
-        <v>-768.6</v>
+        <v>-367.71</v>
       </c>
       <c r="E97" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F97" t="n">
-        <v>745</v>
+        <v>540</v>
       </c>
       <c r="G97" t="n">
-        <v>54.8</v>
+        <v>332.36</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1111</v>
+      </c>
+      <c r="L97" t="n">
+        <v>116</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.058</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:40.330</t>
+          <t>2026-05-29 09:41:02.805</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779421962305</v>
+        <v>1780022461290</v>
       </c>
       <c r="C98" t="n">
-        <v>86693</v>
+        <v>84386</v>
       </c>
       <c r="D98" t="n">
-        <v>-556.17</v>
+        <v>-362.33</v>
       </c>
       <c r="E98" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F98" t="n">
-        <v>745</v>
+        <v>540</v>
       </c>
       <c r="G98" t="n">
-        <v>54.8</v>
+        <v>332.36</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1513</v>
+      </c>
+      <c r="L98" t="n">
+        <v>115</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.175</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:40.626</t>
+          <t>2026-05-29 09:41:02.807</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779421962507</v>
+        <v>1780022461509</v>
       </c>
       <c r="C99" t="n">
-        <v>86861</v>
+        <v>84261</v>
       </c>
       <c r="D99" t="n">
-        <v>-360.36</v>
+        <v>-469.21</v>
       </c>
       <c r="E99" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F99" t="n">
-        <v>745</v>
+        <v>540</v>
       </c>
       <c r="G99" t="n">
-        <v>54.8</v>
+        <v>332.36</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1296</v>
+      </c>
+      <c r="L99" t="n">
+        <v>114</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.785</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:40.627</t>
+          <t>2026-05-29 09:41:02.809</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779421962708</v>
+        <v>1780022461709</v>
       </c>
       <c r="C100" t="n">
-        <v>86172</v>
+        <v>84365</v>
       </c>
       <c r="D100" t="n">
-        <v>-1031.35</v>
+        <v>-341.75</v>
       </c>
       <c r="E100" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F100" t="n">
-        <v>745</v>
+        <v>540</v>
       </c>
       <c r="G100" t="n">
-        <v>54.8</v>
+        <v>332.36</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1099</v>
+      </c>
+      <c r="L100" t="n">
+        <v>105</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.141</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:40.627</t>
+          <t>2026-05-29 09:41:02.962</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779421962910</v>
+        <v>1780022461909</v>
       </c>
       <c r="C101" t="n">
-        <v>86561</v>
+        <v>84383</v>
       </c>
       <c r="D101" t="n">
-        <v>-590.78</v>
+        <v>-306.66</v>
       </c>
       <c r="E101" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F101" t="n">
-        <v>745</v>
+        <v>540</v>
       </c>
       <c r="G101" t="n">
-        <v>54.8</v>
+        <v>332.36</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1052</v>
+      </c>
+      <c r="L101" t="n">
+        <v>113</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.286</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:41.046</t>
+          <t>2026-05-29 09:41:02.965</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779421963111</v>
+        <v>1780022462109</v>
       </c>
       <c r="C102" t="n">
-        <v>86912</v>
+        <v>84185</v>
       </c>
       <c r="D102" t="n">
-        <v>-210.24</v>
+        <v>-489.33</v>
       </c>
       <c r="E102" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="F102" t="n">
-        <v>745</v>
+        <v>540</v>
       </c>
       <c r="G102" t="n">
-        <v>54.8</v>
+        <v>332.36</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K102" t="n">
+        <v>854</v>
+      </c>
+      <c r="L102" t="n">
+        <v>106</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1.789</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:41.047</t>
+          <t>2026-05-29 09:41:03.388</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779421963312</v>
+        <v>1780022462309</v>
       </c>
       <c r="C103" t="n">
-        <v>86589</v>
+        <v>84273</v>
       </c>
       <c r="D103" t="n">
-        <v>-522.73</v>
+        <v>-376.86</v>
       </c>
       <c r="E103" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F103" t="n">
-        <v>1289</v>
+        <v>540</v>
       </c>
       <c r="G103" t="n">
-        <v>197.86</v>
+        <v>332.36</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1078</v>
+      </c>
+      <c r="L103" t="n">
+        <v>115</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.145</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:41.591</t>
+          <t>2026-05-29 09:41:03.403</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779421963514</v>
+        <v>1780022462509</v>
       </c>
       <c r="C104" t="n">
-        <v>86568</v>
+        <v>84208</v>
       </c>
       <c r="D104" t="n">
-        <v>-517.59</v>
+        <v>-423.02</v>
       </c>
       <c r="E104" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F104" t="n">
-        <v>1289</v>
+        <v>540</v>
       </c>
       <c r="G104" t="n">
-        <v>197.86</v>
+        <v>332.36</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K104" t="n">
+        <v>893</v>
+      </c>
+      <c r="L104" t="n">
+        <v>107</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1.241</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:41.591</t>
+          <t>2026-05-29 09:41:03.853</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779421963715</v>
+        <v>1780022462709</v>
       </c>
       <c r="C105" t="n">
-        <v>86868</v>
+        <v>84230</v>
       </c>
       <c r="D105" t="n">
-        <v>-191.71</v>
+        <v>-379.87</v>
       </c>
       <c r="E105" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F105" t="n">
-        <v>1289</v>
+        <v>540</v>
       </c>
       <c r="G105" t="n">
-        <v>197.86</v>
+        <v>332.36</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1143</v>
+      </c>
+      <c r="L105" t="n">
+        <v>111</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1.203</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:41.854</t>
+          <t>2026-05-29 09:41:03.915</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779421963917</v>
+        <v>1780022462909</v>
       </c>
       <c r="C106" t="n">
-        <v>87187</v>
+        <v>84427</v>
       </c>
       <c r="D106" t="n">
-        <v>136.87</v>
+        <v>-163.87</v>
       </c>
       <c r="E106" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F106" t="n">
-        <v>645</v>
+        <v>540</v>
       </c>
       <c r="G106" t="n">
-        <v>196.54</v>
+        <v>332.36</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1005</v>
+      </c>
+      <c r="L106" t="n">
+        <v>104</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.273</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:41.855</t>
+          <t>2026-05-29 09:41:04.293</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779421964118</v>
+        <v>1780022463128</v>
       </c>
       <c r="C107" t="n">
-        <v>86035</v>
+        <v>84152</v>
       </c>
       <c r="D107" t="n">
-        <v>-1021.97</v>
+        <v>-430.68</v>
       </c>
       <c r="E107" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F107" t="n">
-        <v>645</v>
+        <v>2679</v>
       </c>
       <c r="G107" t="n">
-        <v>196.54</v>
+        <v>332.36</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1163</v>
+      </c>
+      <c r="L107" t="n">
+        <v>114</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.996</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:42.311</t>
+          <t>2026-05-29 09:41:04.294</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779421964319</v>
+        <v>1780022463328</v>
       </c>
       <c r="C108" t="n">
-        <v>86593</v>
+        <v>84049</v>
       </c>
       <c r="D108" t="n">
-        <v>-412.87</v>
+        <v>-512.15</v>
       </c>
       <c r="E108" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F108" t="n">
-        <v>645</v>
+        <v>2679</v>
       </c>
       <c r="G108" t="n">
-        <v>196.54</v>
+        <v>332.36</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K108" t="n">
+        <v>965</v>
+      </c>
+      <c r="L108" t="n">
+        <v>107</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:42.312</t>
+          <t>2026-05-29 09:41:04.631</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779421964521</v>
+        <v>1780022463528</v>
       </c>
       <c r="C109" t="n">
-        <v>86897</v>
+        <v>83916</v>
       </c>
       <c r="D109" t="n">
-        <v>-88.23</v>
+        <v>-619.54</v>
       </c>
       <c r="E109" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F109" t="n">
-        <v>645</v>
+        <v>2679</v>
       </c>
       <c r="G109" t="n">
-        <v>196.54</v>
+        <v>332.36</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1101</v>
+      </c>
+      <c r="L109" t="n">
+        <v>109</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.211</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:42.672</t>
+          <t>2026-05-29 09:41:04.633</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779421964722</v>
+        <v>1780022463728</v>
       </c>
       <c r="C110" t="n">
-        <v>86272</v>
+        <v>84115</v>
       </c>
       <c r="D110" t="n">
-        <v>-708.8200000000001</v>
+        <v>-389.56</v>
       </c>
       <c r="E110" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F110" t="n">
-        <v>745</v>
+        <v>2679</v>
       </c>
       <c r="G110" t="n">
-        <v>195.99</v>
+        <v>332.36</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K110" t="n">
+        <v>904</v>
+      </c>
+      <c r="L110" t="n">
+        <v>114</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.122</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:42.673</t>
+          <t>2026-05-29 09:41:05.015</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779421964924</v>
+        <v>1780022463929</v>
       </c>
       <c r="C111" t="n">
-        <v>86482</v>
+        <v>84125</v>
       </c>
       <c r="D111" t="n">
-        <v>-463.38</v>
+        <v>-360.08</v>
       </c>
       <c r="E111" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F111" t="n">
-        <v>745</v>
+        <v>2679</v>
       </c>
       <c r="G111" t="n">
-        <v>195.99</v>
+        <v>332.36</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1085</v>
+      </c>
+      <c r="L111" t="n">
+        <v>107</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.964</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:44.402</t>
+          <t>2026-05-29 09:41:05.017</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779421965125</v>
+        <v>1780022464128</v>
       </c>
       <c r="C112" t="n">
-        <v>86722</v>
+        <v>84173</v>
       </c>
       <c r="D112" t="n">
-        <v>-200.21</v>
+        <v>-294.08</v>
       </c>
       <c r="E112" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F112" t="n">
-        <v>745</v>
+        <v>919</v>
       </c>
       <c r="G112" t="n">
-        <v>195.99</v>
+        <v>305.68</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K112" t="n">
+        <v>888</v>
+      </c>
+      <c r="L112" t="n">
+        <v>106</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.886</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:44.462</t>
+          <t>2026-05-29 09:41:05.364</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779421965326</v>
+        <v>1780022464329</v>
       </c>
       <c r="C113" t="n">
-        <v>87000</v>
+        <v>83936</v>
       </c>
       <c r="D113" t="n">
-        <v>87.8</v>
+        <v>-516.38</v>
       </c>
       <c r="E113" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F113" t="n">
-        <v>685</v>
+        <v>919</v>
       </c>
       <c r="G113" t="n">
-        <v>196.97</v>
+        <v>305.68</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1034</v>
+      </c>
+      <c r="L113" t="n">
+        <v>132</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1.142</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:44.462</t>
+          <t>2026-05-29 09:41:05.365</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779421965528</v>
+        <v>1780022464528</v>
       </c>
       <c r="C114" t="n">
-        <v>86280</v>
+        <v>83727</v>
       </c>
       <c r="D114" t="n">
-        <v>-636.59</v>
+        <v>-699.5599999999999</v>
       </c>
       <c r="E114" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F114" t="n">
-        <v>685</v>
+        <v>919</v>
       </c>
       <c r="G114" t="n">
-        <v>196.97</v>
+        <v>305.68</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K114" t="n">
+        <v>836</v>
+      </c>
+      <c r="L114" t="n">
+        <v>113</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.251</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:44.463</t>
+          <t>2026-05-29 09:41:05.593</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779421965729</v>
+        <v>1780022464728</v>
       </c>
       <c r="C115" t="n">
-        <v>86611</v>
+        <v>83590</v>
       </c>
       <c r="D115" t="n">
-        <v>-273.76</v>
+        <v>-801.58</v>
       </c>
       <c r="E115" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F115" t="n">
-        <v>685</v>
+        <v>919</v>
       </c>
       <c r="G115" t="n">
-        <v>196.97</v>
+        <v>305.68</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K115" t="n">
+        <v>863</v>
+      </c>
+      <c r="L115" t="n">
+        <v>110</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.37</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:44.464</t>
+          <t>2026-05-29 09:41:06.403</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779421965931</v>
+        <v>1780022464947</v>
       </c>
       <c r="C116" t="n">
-        <v>86905</v>
+        <v>83589</v>
       </c>
       <c r="D116" t="n">
-        <v>33.93</v>
+        <v>-762.5</v>
       </c>
       <c r="E116" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="F116" t="n">
-        <v>684</v>
+        <v>919</v>
       </c>
       <c r="G116" t="n">
-        <v>197.81</v>
+        <v>305.68</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1455</v>
+      </c>
+      <c r="L116" t="n">
+        <v>115</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.267</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:44.465</t>
+          <t>2026-05-29 09:41:06.405</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779421966132</v>
+        <v>1780022465147</v>
       </c>
       <c r="C117" t="n">
-        <v>86295</v>
+        <v>83974</v>
       </c>
       <c r="D117" t="n">
-        <v>-577.77</v>
+        <v>-339.38</v>
       </c>
       <c r="E117" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="F117" t="n">
-        <v>684</v>
+        <v>919</v>
       </c>
       <c r="G117" t="n">
-        <v>197.81</v>
+        <v>305.68</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1257</v>
+      </c>
+      <c r="L117" t="n">
+        <v>115</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.014</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:44.465</t>
+          <t>2026-05-29 09:41:06.406</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779421966333</v>
+        <v>1780022465347</v>
       </c>
       <c r="C118" t="n">
-        <v>86591</v>
+        <v>84575</v>
       </c>
       <c r="D118" t="n">
-        <v>-252.88</v>
+        <v>278.59</v>
       </c>
       <c r="E118" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F118" t="n">
-        <v>684</v>
+        <v>1259</v>
       </c>
       <c r="G118" t="n">
-        <v>197.81</v>
+        <v>288.01</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J118" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1058</v>
+      </c>
+      <c r="L118" t="n">
+        <v>118</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.019</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:44.466</t>
+          <t>2026-05-29 09:41:06.407</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779421966535</v>
+        <v>1780022465547</v>
       </c>
       <c r="C119" t="n">
-        <v>86632</v>
+        <v>84752</v>
       </c>
       <c r="D119" t="n">
-        <v>-199.23</v>
+        <v>441.66</v>
       </c>
       <c r="E119" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F119" t="n">
-        <v>684</v>
+        <v>1259</v>
       </c>
       <c r="G119" t="n">
-        <v>197.81</v>
+        <v>288.01</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J119" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K119" t="n">
+        <v>859</v>
+      </c>
+      <c r="L119" t="n">
+        <v>117</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.887</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:44.719</t>
+          <t>2026-05-29 09:41:06.907</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779421966736</v>
+        <v>1780022465747</v>
       </c>
       <c r="C120" t="n">
-        <v>86879</v>
+        <v>84901</v>
       </c>
       <c r="D120" t="n">
-        <v>57.73</v>
+        <v>568.58</v>
       </c>
       <c r="E120" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F120" t="n">
-        <v>705</v>
+        <v>1259</v>
       </c>
       <c r="G120" t="n">
-        <v>196.5</v>
+        <v>288.01</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L120" t="n">
+        <v>117</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.903</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:44.720</t>
+          <t>2026-05-29 09:41:06.943</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779421966938</v>
+        <v>1780022465947</v>
       </c>
       <c r="C121" t="n">
-        <v>86080</v>
+        <v>84435</v>
       </c>
       <c r="D121" t="n">
-        <v>-744.16</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="E121" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F121" t="n">
-        <v>705</v>
+        <v>1259</v>
       </c>
       <c r="G121" t="n">
-        <v>196.5</v>
+        <v>288.01</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>995</v>
+      </c>
+      <c r="L121" t="n">
+        <v>123</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.019</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:45.260</t>
+          <t>2026-05-29 09:41:07.220</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779421967139</v>
+        <v>1780022466147</v>
       </c>
       <c r="C122" t="n">
-        <v>86342</v>
+        <v>84537</v>
       </c>
       <c r="D122" t="n">
-        <v>-444.95</v>
+        <v>172.44</v>
       </c>
       <c r="E122" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F122" t="n">
-        <v>705</v>
+        <v>1259</v>
       </c>
       <c r="G122" t="n">
-        <v>196.5</v>
+        <v>288.01</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1072</v>
+      </c>
+      <c r="L122" t="n">
+        <v>123</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:45.266</t>
+          <t>2026-05-29 09:41:07.221</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779421967340</v>
+        <v>1780022466347</v>
       </c>
       <c r="C123" t="n">
-        <v>86851</v>
+        <v>85487</v>
       </c>
       <c r="D123" t="n">
-        <v>86.3</v>
+        <v>1113.82</v>
       </c>
       <c r="E123" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="F123" t="n">
-        <v>705</v>
+        <v>1120</v>
       </c>
       <c r="G123" t="n">
-        <v>196.5</v>
+        <v>252.2</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K123" t="n">
+        <v>873</v>
+      </c>
+      <c r="L123" t="n">
+        <v>114</v>
+      </c>
+      <c r="M123" t="n">
+        <v>1.119</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:45.591</t>
+          <t>2026-05-29 09:41:08.756</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779421967542</v>
+        <v>1780022466566</v>
       </c>
       <c r="C124" t="n">
-        <v>86174</v>
+        <v>86605</v>
       </c>
       <c r="D124" t="n">
-        <v>-595.02</v>
+        <v>2176.13</v>
       </c>
       <c r="E124" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="F124" t="n">
-        <v>746</v>
+        <v>1120</v>
       </c>
       <c r="G124" t="n">
-        <v>194.58</v>
+        <v>252.2</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K124" t="n">
+        <v>2188</v>
+      </c>
+      <c r="L124" t="n">
+        <v>121</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.185</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:45.591</t>
+          <t>2026-05-29 09:41:08.758</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779421967743</v>
+        <v>1780022466766</v>
       </c>
       <c r="C125" t="n">
-        <v>86574</v>
+        <v>86455</v>
       </c>
       <c r="D125" t="n">
-        <v>-165.27</v>
+        <v>1917.32</v>
       </c>
       <c r="E125" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="F125" t="n">
-        <v>746</v>
+        <v>1120</v>
       </c>
       <c r="G125" t="n">
-        <v>194.58</v>
+        <v>252.2</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1991</v>
+      </c>
+      <c r="L125" t="n">
+        <v>123</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.002</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:45.951</t>
+          <t>2026-05-29 09:41:08.759</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779421967945</v>
+        <v>1780022466967</v>
       </c>
       <c r="C126" t="n">
-        <v>86870</v>
+        <v>85660</v>
       </c>
       <c r="D126" t="n">
-        <v>139</v>
+        <v>1026.46</v>
       </c>
       <c r="E126" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F126" t="n">
-        <v>584</v>
+        <v>1120</v>
       </c>
       <c r="G126" t="n">
-        <v>196.35</v>
+        <v>252.2</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1791</v>
+      </c>
+      <c r="L126" t="n">
+        <v>108</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.649</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:45.952</t>
+          <t>2026-05-29 09:41:08.760</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779421968146</v>
+        <v>1780022467166</v>
       </c>
       <c r="C127" t="n">
-        <v>87106</v>
+        <v>85748</v>
       </c>
       <c r="D127" t="n">
-        <v>368.05</v>
+        <v>1063.14</v>
       </c>
       <c r="E127" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F127" t="n">
-        <v>584</v>
+        <v>1120</v>
       </c>
       <c r="G127" t="n">
-        <v>196.35</v>
+        <v>252.2</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1594</v>
+      </c>
+      <c r="L127" t="n">
+        <v>118</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:46.415</t>
+          <t>2026-05-29 09:41:08.761</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779421968347</v>
+        <v>1780022467366</v>
       </c>
       <c r="C128" t="n">
-        <v>86522</v>
+        <v>85719</v>
       </c>
       <c r="D128" t="n">
-        <v>-234.36</v>
+        <v>980.98</v>
       </c>
       <c r="E128" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F128" t="n">
-        <v>584</v>
+        <v>1120</v>
       </c>
       <c r="G128" t="n">
-        <v>196.35</v>
+        <v>252.2</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1395</v>
+      </c>
+      <c r="L128" t="n">
+        <v>107</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.646</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:46.416</t>
+          <t>2026-05-29 09:41:08.762</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779421968549</v>
+        <v>1780022467566</v>
       </c>
       <c r="C129" t="n">
-        <v>86821</v>
+        <v>85156</v>
       </c>
       <c r="D129" t="n">
-        <v>76.36</v>
+        <v>368.93</v>
       </c>
       <c r="E129" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F129" t="n">
-        <v>584</v>
+        <v>1120</v>
       </c>
       <c r="G129" t="n">
-        <v>196.35</v>
+        <v>252.2</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L129" t="n">
+        <v>112</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.6889999999999999</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:46.807</t>
+          <t>2026-05-29 09:41:08.926</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779421968750</v>
+        <v>1780022467767</v>
       </c>
       <c r="C130" t="n">
-        <v>87244</v>
+        <v>84393</v>
       </c>
       <c r="D130" t="n">
-        <v>495.54</v>
+        <v>-412.52</v>
       </c>
       <c r="E130" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F130" t="n">
-        <v>725</v>
+        <v>1120</v>
       </c>
       <c r="G130" t="n">
-        <v>194.4</v>
+        <v>252.2</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1157</v>
+      </c>
+      <c r="L130" t="n">
+        <v>107</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.105</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:46.808</t>
+          <t>2026-05-29 09:41:08.994</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779421968952</v>
+        <v>1780022467966</v>
       </c>
       <c r="C131" t="n">
-        <v>86522</v>
+        <v>83960</v>
       </c>
       <c r="D131" t="n">
-        <v>-251.23</v>
+        <v>-824.89</v>
       </c>
       <c r="E131" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F131" t="n">
-        <v>725</v>
+        <v>1120</v>
       </c>
       <c r="G131" t="n">
-        <v>194.4</v>
+        <v>252.2</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1027</v>
+      </c>
+      <c r="L131" t="n">
+        <v>122</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.93</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:47.382</t>
+          <t>2026-05-29 09:41:09.034</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779421969153</v>
+        <v>1780022468167</v>
       </c>
       <c r="C132" t="n">
-        <v>86926</v>
+        <v>84009</v>
       </c>
       <c r="D132" t="n">
-        <v>165.33</v>
+        <v>-734.65</v>
       </c>
       <c r="E132" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F132" t="n">
-        <v>725</v>
+        <v>1120</v>
       </c>
       <c r="G132" t="n">
-        <v>194.4</v>
+        <v>252.2</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>52</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K132" t="n">
+        <v>866</v>
+      </c>
+      <c r="L132" t="n">
+        <v>105</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.709</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:47.383</t>
+          <t>2026-05-29 09:41:09.367</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1779421969354</v>
+        <v>1780022468385</v>
       </c>
       <c r="C133" t="n">
-        <v>87244</v>
+        <v>83960</v>
       </c>
       <c r="D133" t="n">
-        <v>475.06</v>
+        <v>-746.91</v>
       </c>
       <c r="E133" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F133" t="n">
-        <v>664</v>
+        <v>1120</v>
       </c>
       <c r="G133" t="n">
-        <v>196.55</v>
+        <v>252.2</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K133" t="n">
+        <v>980</v>
+      </c>
+      <c r="L133" t="n">
+        <v>127</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1.677</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:47.384</t>
+          <t>2026-05-29 09:41:09.896</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1779421969556</v>
+        <v>1780022468586</v>
       </c>
       <c r="C134" t="n">
-        <v>87046</v>
+        <v>84356</v>
       </c>
       <c r="D134" t="n">
-        <v>253.31</v>
+        <v>-313.57</v>
       </c>
       <c r="E134" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F134" t="n">
-        <v>664</v>
+        <v>1120</v>
       </c>
       <c r="G134" t="n">
-        <v>196.55</v>
+        <v>252.2</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="J134" t="n">
+        <v>35.27</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1309</v>
+      </c>
+      <c r="L134" t="n">
+        <v>107</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1.093</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:47.817</t>
+          <t>2026-05-29 09:41:09.897</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1779421969757</v>
+        <v>1780022468785</v>
       </c>
       <c r="C135" t="n">
-        <v>86527</v>
+        <v>84247</v>
       </c>
       <c r="D135" t="n">
-        <v>-278.36</v>
+        <v>-406.89</v>
       </c>
       <c r="E135" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F135" t="n">
-        <v>664</v>
+        <v>1120</v>
       </c>
       <c r="G135" t="n">
-        <v>196.55</v>
+        <v>252.2</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1111</v>
+      </c>
+      <c r="L135" t="n">
+        <v>110</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.542</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:47.817</t>
+          <t>2026-05-29 09:41:09.898</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1779421969959</v>
+        <v>1780022468985</v>
       </c>
       <c r="C136" t="n">
-        <v>86824</v>
+        <v>84163</v>
       </c>
       <c r="D136" t="n">
-        <v>32.56</v>
+        <v>-470.55</v>
       </c>
       <c r="E136" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="F136" t="n">
-        <v>664</v>
+        <v>1120</v>
       </c>
       <c r="G136" t="n">
-        <v>196.55</v>
+        <v>252.2</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K136" t="n">
+        <v>912</v>
+      </c>
+      <c r="L136" t="n">
+        <v>109</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.534</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:48.241</t>
+          <t>2026-05-29 09:41:09.898</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1779421970160</v>
+        <v>1780022469185</v>
       </c>
       <c r="C137" t="n">
-        <v>87210</v>
+        <v>84259</v>
       </c>
       <c r="D137" t="n">
-        <v>416.93</v>
+        <v>-351.02</v>
       </c>
       <c r="E137" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F137" t="n">
-        <v>806</v>
+        <v>1120</v>
       </c>
       <c r="G137" t="n">
-        <v>61.71</v>
+        <v>252.2</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K137" t="n">
+        <v>713</v>
+      </c>
+      <c r="L137" t="n">
+        <v>119</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.572</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:48.274</t>
+          <t>2026-05-29 09:41:10.354</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1779421970361</v>
+        <v>1780022469385</v>
       </c>
       <c r="C138" t="n">
-        <v>86637</v>
+        <v>83976</v>
       </c>
       <c r="D138" t="n">
-        <v>-176.91</v>
+        <v>-616.47</v>
       </c>
       <c r="E138" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F138" t="n">
-        <v>806</v>
+        <v>1120</v>
       </c>
       <c r="G138" t="n">
-        <v>61.71</v>
+        <v>252.2</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K138" t="n">
+        <v>968</v>
+      </c>
+      <c r="L138" t="n">
+        <v>144</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.969</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:48.625</t>
+          <t>2026-05-29 09:41:10.355</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1779421970563</v>
+        <v>1780022469585</v>
       </c>
       <c r="C139" t="n">
-        <v>86773</v>
+        <v>84127</v>
       </c>
       <c r="D139" t="n">
-        <v>-32.07</v>
+        <v>-434.64</v>
       </c>
       <c r="E139" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F139" t="n">
-        <v>806</v>
+        <v>1120</v>
       </c>
       <c r="G139" t="n">
-        <v>61.71</v>
+        <v>252.2</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K139" t="n">
+        <v>769</v>
+      </c>
+      <c r="L139" t="n">
+        <v>107</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.909</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:48.626</t>
+          <t>2026-05-29 09:41:11.207</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1779421970764</v>
+        <v>1780022469804</v>
       </c>
       <c r="C140" t="n">
-        <v>87060</v>
+        <v>83948</v>
       </c>
       <c r="D140" t="n">
-        <v>256.54</v>
+        <v>-591.91</v>
       </c>
       <c r="E140" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F140" t="n">
-        <v>806</v>
+        <v>1120</v>
       </c>
       <c r="G140" t="n">
-        <v>61.71</v>
+        <v>252.2</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1402</v>
+      </c>
+      <c r="L140" t="n">
+        <v>115</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1.298</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:49.326</t>
+          <t>2026-05-29 09:41:11.209</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1779421970966</v>
+        <v>1780022470004</v>
       </c>
       <c r="C141" t="n">
-        <v>87388</v>
+        <v>84015</v>
       </c>
       <c r="D141" t="n">
-        <v>571.71</v>
+        <v>-495.32</v>
       </c>
       <c r="E141" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F141" t="n">
-        <v>725</v>
+        <v>1120</v>
       </c>
       <c r="G141" t="n">
-        <v>59.08</v>
+        <v>252.2</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1204</v>
+      </c>
+      <c r="L141" t="n">
+        <v>106</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.915</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:49.327</t>
+          <t>2026-05-29 09:41:11.557</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1779421971167</v>
+        <v>1780022470204</v>
       </c>
       <c r="C142" t="n">
-        <v>86630</v>
+        <v>84364</v>
       </c>
       <c r="D142" t="n">
-        <v>-214.88</v>
+        <v>-121.55</v>
       </c>
       <c r="E142" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F142" t="n">
-        <v>725</v>
+        <v>3877</v>
       </c>
       <c r="G142" t="n">
-        <v>59.08</v>
+        <v>252.2</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1352</v>
+      </c>
+      <c r="L142" t="n">
+        <v>114</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.944</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:49.337</t>
+          <t>2026-05-29 09:41:11.565</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1779421971368</v>
+        <v>1780022470404</v>
       </c>
       <c r="C143" t="n">
-        <v>87049</v>
+        <v>84101</v>
       </c>
       <c r="D143" t="n">
-        <v>214.87</v>
+        <v>-378.47</v>
       </c>
       <c r="E143" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F143" t="n">
-        <v>725</v>
+        <v>3877</v>
       </c>
       <c r="G143" t="n">
-        <v>59.08</v>
+        <v>252.2</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L143" t="n">
+        <v>108</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1.153</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:49.338</t>
+          <t>2026-05-29 09:41:11.620</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1779421971570</v>
+        <v>1780022470604</v>
       </c>
       <c r="C144" t="n">
-        <v>87306</v>
+        <v>88177</v>
       </c>
       <c r="D144" t="n">
-        <v>461.12</v>
+        <v>3716.45</v>
       </c>
       <c r="E144" t="n">
         <v>82</v>
       </c>
       <c r="F144" t="n">
-        <v>725</v>
+        <v>360</v>
       </c>
       <c r="G144" t="n">
-        <v>59.08</v>
+        <v>315.76</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1016</v>
+      </c>
+      <c r="L144" t="n">
+        <v>104</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.595</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:49.683</t>
+          <t>2026-05-29 09:41:11.977</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1779421971771</v>
+        <v>1780022470804</v>
       </c>
       <c r="C145" t="n">
-        <v>87629</v>
+        <v>85521</v>
       </c>
       <c r="D145" t="n">
-        <v>761.0700000000001</v>
+        <v>874.63</v>
       </c>
       <c r="E145" t="n">
         <v>82</v>
       </c>
       <c r="F145" t="n">
-        <v>725</v>
+        <v>360</v>
       </c>
       <c r="G145" t="n">
-        <v>57.97</v>
+        <v>315.76</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J145" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1172</v>
+      </c>
+      <c r="L145" t="n">
+        <v>112</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1.078</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:49.870</t>
+          <t>2026-05-29 09:41:12.039</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1779421971973</v>
+        <v>1780022471004</v>
       </c>
       <c r="C146" t="n">
-        <v>86856</v>
+        <v>84540</v>
       </c>
       <c r="D146" t="n">
-        <v>-49.99</v>
+        <v>-150.1</v>
       </c>
       <c r="E146" t="n">
         <v>82</v>
       </c>
       <c r="F146" t="n">
-        <v>725</v>
+        <v>360</v>
       </c>
       <c r="G146" t="n">
-        <v>57.97</v>
+        <v>315.76</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I146" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J146" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1035</v>
+      </c>
+      <c r="L146" t="n">
+        <v>106</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.553</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:50.269</t>
+          <t>2026-05-29 09:41:12.048</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1779421972174</v>
+        <v>1780022471204</v>
       </c>
       <c r="C147" t="n">
-        <v>87171</v>
+        <v>85853</v>
       </c>
       <c r="D147" t="n">
-        <v>267.51</v>
+        <v>1170.4</v>
       </c>
       <c r="E147" t="n">
         <v>82</v>
       </c>
       <c r="F147" t="n">
-        <v>725</v>
+        <v>360</v>
       </c>
       <c r="G147" t="n">
-        <v>57.97</v>
+        <v>315.76</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I147" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J147" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K147" t="n">
+        <v>843</v>
+      </c>
+      <c r="L147" t="n">
+        <v>104</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.869</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-22 10:52:50.269</t>
+          <t>2026-05-29 09:41:13.058</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1779421972375</v>
+        <v>1780022471423</v>
       </c>
       <c r="C148" t="n">
-        <v>87462</v>
+        <v>87381</v>
       </c>
       <c r="D148" t="n">
-        <v>545.14</v>
+        <v>2639.88</v>
       </c>
       <c r="E148" t="n">
         <v>82</v>
       </c>
       <c r="F148" t="n">
-        <v>725</v>
+        <v>360</v>
       </c>
       <c r="G148" t="n">
-        <v>57.97</v>
+        <v>315.76</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
       </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:52:50.704</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>1779421972577</v>
-      </c>
-      <c r="C149" t="n">
-        <v>87663</v>
-      </c>
-      <c r="D149" t="n">
-        <v>718.88</v>
-      </c>
-      <c r="E149" t="n">
-        <v>78</v>
-      </c>
-      <c r="F149" t="n">
-        <v>806</v>
-      </c>
-      <c r="G149" t="n">
-        <v>65.48999999999999</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:52:50.704</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>1779421972778</v>
-      </c>
-      <c r="C150" t="n">
-        <v>87075</v>
-      </c>
-      <c r="D150" t="n">
-        <v>94.94</v>
-      </c>
-      <c r="E150" t="n">
-        <v>78</v>
-      </c>
-      <c r="F150" t="n">
-        <v>806</v>
-      </c>
-      <c r="G150" t="n">
-        <v>65.48999999999999</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:52:51.530</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>1779421972980</v>
-      </c>
-      <c r="C151" t="n">
-        <v>87590</v>
-      </c>
-      <c r="D151" t="n">
-        <v>605.1900000000001</v>
-      </c>
-      <c r="E151" t="n">
-        <v>78</v>
-      </c>
-      <c r="F151" t="n">
-        <v>806</v>
-      </c>
-      <c r="G151" t="n">
-        <v>65.48999999999999</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="I148" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J148" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1634</v>
+      </c>
+      <c r="L148" t="n">
+        <v>110</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0.876</v>
       </c>
     </row>
   </sheetData>
